--- a/data/gold/tabela_conversao_linguagem_cliente.xlsx
+++ b/data/gold/tabela_conversao_linguagem_cliente.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabalho\Ciência de Dados\Material\Projetos III\NorthData-Consulting-Classific-ESG-por-Machine-Learning\data\gold\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58207E5E-0471-48CE-B759-2EF4B1ABA4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DD3675-DCFE-411D-BB53-7F062A8A0986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{5993AD73-4C1F-4C74-8F78-5A222A3B76DD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{5993AD73-4C1F-4C74-8F78-5A222A3B76DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Equivalências colunas" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="154">
   <si>
     <t>cik</t>
   </si>
@@ -107,9 +107,6 @@
     <t>nome</t>
   </si>
   <si>
-    <t>bolsa</t>
-  </si>
-  <si>
     <t>setor</t>
   </si>
   <si>
@@ -486,6 +483,21 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>perfil</t>
+  </si>
+  <si>
+    <t>Tradicional</t>
+  </si>
+  <si>
+    <t>Inovador</t>
+  </si>
+  <si>
+    <t>NYSE</t>
+  </si>
+  <si>
+    <t>NASDAQ</t>
   </si>
 </sst>
 </file>
@@ -860,7 +872,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -881,7 +893,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>149</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
@@ -889,7 +901,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
@@ -897,7 +909,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
@@ -905,7 +917,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
@@ -913,7 +925,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -921,7 +933,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
@@ -929,7 +941,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
@@ -937,7 +949,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
@@ -945,7 +957,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
@@ -953,7 +965,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -961,7 +973,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -969,7 +981,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -977,7 +989,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
@@ -985,7 +997,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
         <v>16</v>
@@ -993,7 +1005,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
         <v>17</v>
@@ -1006,372 +1018,392 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D29B8487-8004-42BF-AD46-0D562B524988}">
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="37.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.7265625" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>83</v>
       </c>
-      <c r="B2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>84</v>
       </c>
-      <c r="B3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>85</v>
       </c>
-      <c r="B4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>86</v>
       </c>
-      <c r="B5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>87</v>
       </c>
-      <c r="B6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>88</v>
       </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>89</v>
       </c>
-      <c r="B8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>90</v>
       </c>
-      <c r="B9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>91</v>
       </c>
-      <c r="B10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>92</v>
       </c>
-      <c r="B11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>93</v>
       </c>
-      <c r="B12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>94</v>
       </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>95</v>
       </c>
-      <c r="B14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>96</v>
       </c>
-      <c r="B15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>97</v>
-      </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B33" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1393,131 +1425,131 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" t="s">
         <v>135</v>
-      </c>
-      <c r="C1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" t="s">
         <v>131</v>
       </c>
-      <c r="B8" t="s">
-        <v>149</v>
-      </c>
-      <c r="C8" t="s">
-        <v>132</v>
-      </c>
       <c r="D8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
